--- a/PFP-C/Input data and Generated Schedule/123.xlsx
+++ b/PFP-C/Input data and Generated Schedule/123.xlsx
@@ -47339,7 +47339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47364,7 +47364,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -47374,7 +47374,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -47384,11 +47384,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>85.21300000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -68279,7 +68399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68315,25 +68435,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -68366,18 +68481,15 @@
         <v>3.578947368421048</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>255.6418918918919</v>
       </c>
       <c r="I2" t="n">
-        <v>255.6418918918919</v>
+        <v>1.531531531531529</v>
       </c>
       <c r="J2" t="n">
-        <v>1.531531531531529</v>
-      </c>
-      <c r="K2" t="n">
         <v>0.5990925509889424</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68410,18 +68522,15 @@
         <v>5.357142857142875</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>287.7357357357357</v>
       </c>
       <c r="I3" t="n">
-        <v>287.7357357357357</v>
+        <v>2.702702702702712</v>
       </c>
       <c r="J3" t="n">
-        <v>2.702702702702712</v>
-      </c>
-      <c r="K3" t="n">
         <v>0.939300325624116</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68454,18 +68563,15 @@
         <v>4.98886414253898</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>398.4617117117117</v>
       </c>
       <c r="I4" t="n">
-        <v>398.4617117117117</v>
+        <v>3.363363363363366</v>
       </c>
       <c r="J4" t="n">
-        <v>3.363363363363366</v>
-      </c>
-      <c r="K4" t="n">
         <v>0.8440869635667203</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68498,18 +68604,15 @@
         <v>8.199999999999985</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>431.1561561561561</v>
       </c>
       <c r="I5" t="n">
-        <v>431.1561561561561</v>
+        <v>6.156156156156144</v>
       </c>
       <c r="J5" t="n">
-        <v>6.156156156156144</v>
-      </c>
-      <c r="K5" t="n">
         <v>1.427825178478145</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68542,18 +68645,15 @@
         <v>3.684210526315788</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>250.5367867867868</v>
       </c>
       <c r="I6" t="n">
-        <v>250.5367867867868</v>
+        <v>1.576576576576576</v>
       </c>
       <c r="J6" t="n">
-        <v>1.576576576576576</v>
-      </c>
-      <c r="K6" t="n">
         <v>0.6292794750011235</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68586,18 +68686,15 @@
         <v>6.328124999999986</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>331.8438438438437</v>
       </c>
       <c r="I7" t="n">
-        <v>331.8438438438437</v>
+        <v>3.64864864864864</v>
       </c>
       <c r="J7" t="n">
-        <v>3.64864864864864</v>
-      </c>
-      <c r="K7" t="n">
         <v>1.099507710128138</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68630,18 +68727,15 @@
         <v>9.999999999999973</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>341.4534534534534</v>
       </c>
       <c r="I8" t="n">
-        <v>341.4534534534534</v>
+        <v>5.76576576576575</v>
       </c>
       <c r="J8" t="n">
-        <v>5.76576576576575</v>
-      </c>
-      <c r="K8" t="n">
         <v>1.688594948286775</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68674,18 +68768,15 @@
         <v>5.231143552311432</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>374.7665165165165</v>
       </c>
       <c r="I9" t="n">
-        <v>374.7665165165165</v>
+        <v>3.228228228228226</v>
       </c>
       <c r="J9" t="n">
-        <v>3.228228228228226</v>
-      </c>
-      <c r="K9" t="n">
         <v>0.8613971862360743</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68718,18 +68809,15 @@
         <v>4.594594594594581</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>287.4376876876877</v>
       </c>
       <c r="I10" t="n">
-        <v>287.4376876876877</v>
+        <v>2.297297297297291</v>
       </c>
       <c r="J10" t="n">
-        <v>2.297297297297291</v>
-      </c>
-      <c r="K10" t="n">
         <v>0.7992331540717773</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68762,18 +68850,15 @@
         <v>9.999999999999973</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>338.4504504504505</v>
       </c>
       <c r="I11" t="n">
-        <v>338.4504504504505</v>
+        <v>5.76576576576575</v>
       </c>
       <c r="J11" t="n">
-        <v>5.76576576576575</v>
-      </c>
-      <c r="K11" t="n">
         <v>1.703577512776826</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68806,18 +68891,15 @@
         <v>7.872340425531918</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>374.7575075075075</v>
       </c>
       <c r="I12" t="n">
-        <v>374.7575075075075</v>
+        <v>5.000000000000003</v>
       </c>
       <c r="J12" t="n">
-        <v>5.000000000000003</v>
-      </c>
-      <c r="K12" t="n">
         <v>1.334196086758806</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -68850,18 +68932,15 @@
         <v>7.861915367483291</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>390.3536036036036</v>
       </c>
       <c r="I13" t="n">
-        <v>390.3536036036036</v>
+        <v>5.300300300300296</v>
       </c>
       <c r="J13" t="n">
-        <v>5.300300300300296</v>
-      </c>
-      <c r="K13" t="n">
         <v>1.35782025613952</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -68894,18 +68973,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.77865006333445</v>
+        <v>278.1426426426426</v>
       </c>
       <c r="I14" t="n">
-        <v>278.1426426426426</v>
+        <v>4.714714714714709</v>
       </c>
       <c r="J14" t="n">
-        <v>4.714714714714709</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.695070798896583</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68938,18 +69014,15 @@
         <v>8.895184135977338</v>
       </c>
       <c r="H15" t="n">
-        <v>-5.896774908809107</v>
+        <v>303.0382882882883</v>
       </c>
       <c r="I15" t="n">
-        <v>303.0382882882883</v>
+        <v>4.714714714714715</v>
       </c>
       <c r="J15" t="n">
-        <v>4.714714714714715</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.555814858031894</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -68982,18 +69055,15 @@
         <v>6.84895833333332</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>339.0510510510509</v>
       </c>
       <c r="I16" t="n">
-        <v>339.0510510510509</v>
+        <v>3.94894894894894</v>
       </c>
       <c r="J16" t="n">
-        <v>3.94894894894894</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.164706299156804</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69026,18 +69096,15 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
+        <v>185.4151651651651</v>
+      </c>
+      <c r="I17" t="n">
         <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>185.4151651651651</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69070,18 +69137,15 @@
         <v>6.607142857142868</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>301.5495495495496</v>
       </c>
       <c r="I18" t="n">
-        <v>301.5495495495496</v>
+        <v>3.333333333333339</v>
       </c>
       <c r="J18" t="n">
-        <v>3.333333333333339</v>
-      </c>
-      <c r="K18" t="n">
         <v>1.105401529636713</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69114,18 +69178,15 @@
         <v>3.885350318471348</v>
       </c>
       <c r="H19" t="n">
-        <v>-27.51790088311122</v>
+        <v>262.527027027027</v>
       </c>
       <c r="I19" t="n">
-        <v>262.527027027027</v>
+        <v>1.831831831831837</v>
       </c>
       <c r="J19" t="n">
-        <v>1.831831831831837</v>
-      </c>
-      <c r="K19" t="n">
         <v>0.6977688554874963</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69158,18 +69219,15 @@
         <v>4.255319148936184</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>371.1539039039039</v>
       </c>
       <c r="I20" t="n">
-        <v>371.1539039039039</v>
+        <v>2.702702702702712</v>
       </c>
       <c r="J20" t="n">
-        <v>2.702702702702712</v>
-      </c>
-      <c r="K20" t="n">
         <v>0.7281892159222642</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69202,18 +69260,15 @@
         <v>8.640226628895176</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9842402576911695</v>
+        <v>303.0382882882883</v>
       </c>
       <c r="I21" t="n">
-        <v>303.0382882882883</v>
+        <v>4.579579579579575</v>
       </c>
       <c r="J21" t="n">
-        <v>4.579579579579575</v>
-      </c>
-      <c r="K21" t="n">
         <v>1.511221438534163</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69246,18 +69301,15 @@
         <v>7.839999999999988</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>440.7657657657658</v>
       </c>
       <c r="I22" t="n">
-        <v>440.7657657657658</v>
+        <v>5.885885885885878</v>
       </c>
       <c r="J22" t="n">
-        <v>5.885885885885878</v>
-      </c>
-      <c r="K22" t="n">
         <v>1.335377278146821</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69290,18 +69342,15 @@
         <v>9.21999999999997</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>450.0750750750751</v>
       </c>
       <c r="I23" t="n">
-        <v>450.0750750750751</v>
+        <v>6.921921921921899</v>
       </c>
       <c r="J23" t="n">
-        <v>6.921921921921899</v>
-      </c>
-      <c r="K23" t="n">
         <v>1.537948290241863</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69334,18 +69383,15 @@
         <v>2.607526881720429</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>310.5315315315315</v>
       </c>
       <c r="I24" t="n">
-        <v>310.5315315315315</v>
+        <v>1.456456456456456</v>
       </c>
       <c r="J24" t="n">
-        <v>1.456456456456456</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.4690204725018615</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69378,18 +69424,15 @@
         <v>6.958637469586364</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>366.0578078078078</v>
       </c>
       <c r="I25" t="n">
-        <v>366.0578078078078</v>
+        <v>4.294294294294287</v>
       </c>
       <c r="J25" t="n">
-        <v>4.294294294294287</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.173119163885976</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69422,18 +69465,15 @@
         <v>7.639902676399027</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>365.7575075075074</v>
       </c>
       <c r="I26" t="n">
-        <v>365.7575075075074</v>
+        <v>4.714714714714715</v>
       </c>
       <c r="J26" t="n">
-        <v>4.714714714714715</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.289027461621671</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69466,18 +69506,15 @@
         <v>9.999999999999989</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>261.3475975975975</v>
       </c>
       <c r="I27" t="n">
-        <v>261.3475975975975</v>
+        <v>4.279279279279274</v>
       </c>
       <c r="J27" t="n">
-        <v>4.279279279279274</v>
-      </c>
-      <c r="K27" t="n">
         <v>1.637389942978612</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69510,18 +69547,15 @@
         <v>5.127388535031848</v>
       </c>
       <c r="H28" t="n">
-        <v>-21.87989662731752</v>
+        <v>274.2387387387387</v>
       </c>
       <c r="I28" t="n">
-        <v>274.2387387387387</v>
+        <v>2.417417417417417</v>
       </c>
       <c r="J28" t="n">
-        <v>2.417417417417417</v>
-      </c>
-      <c r="K28" t="n">
         <v>0.881501070394157</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69554,18 +69588,15 @@
         <v>3.885350318471348</v>
       </c>
       <c r="H29" t="n">
-        <v>-13.66270653556626</v>
+        <v>278.4429429429429</v>
       </c>
       <c r="I29" t="n">
-        <v>278.4429429429429</v>
+        <v>1.831831831831837</v>
       </c>
       <c r="J29" t="n">
-        <v>1.831831831831837</v>
-      </c>
-      <c r="K29" t="n">
         <v>0.6578840937646626</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69598,18 +69629,15 @@
         <v>1.411192214111918</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>355.5472972972973</v>
       </c>
       <c r="I30" t="n">
-        <v>355.5472972972973</v>
+        <v>0.8708708708708682</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8708708708708682</v>
-      </c>
-      <c r="K30" t="n">
         <v>0.2449381214512999</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69642,18 +69670,15 @@
         <v>9.239999999999995</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>446.1711711711712</v>
       </c>
       <c r="I31" t="n">
-        <v>446.1711711711712</v>
+        <v>6.936936936936933</v>
       </c>
       <c r="J31" t="n">
-        <v>6.936936936936933</v>
-      </c>
-      <c r="K31" t="n">
         <v>1.5547703180212</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69686,18 +69711,15 @@
         <v>8.978102189781016</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>359.7515015015015</v>
       </c>
       <c r="I32" t="n">
-        <v>359.7515015015015</v>
+        <v>5.540540540540537</v>
       </c>
       <c r="J32" t="n">
-        <v>5.540540540540537</v>
-      </c>
-      <c r="K32" t="n">
         <v>1.540102130891985</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -69730,18 +69752,15 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>335.7424924924925</v>
       </c>
       <c r="I33" t="n">
-        <v>335.7424924924925</v>
+        <v>5.870870870870871</v>
       </c>
       <c r="J33" t="n">
-        <v>5.870870870870871</v>
-      </c>
-      <c r="K33" t="n">
         <v>1.748623126994314</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69774,18 +69793,15 @@
         <v>8.794326241134748</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>361.5442942942943</v>
       </c>
       <c r="I34" t="n">
-        <v>361.5442942942943</v>
+        <v>5.585585585585584</v>
       </c>
       <c r="J34" t="n">
-        <v>5.585585585585584</v>
-      </c>
-      <c r="K34" t="n">
         <v>1.544924280021678</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69818,18 +69834,15 @@
         <v>6.964285714285701</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>279.6276276276276</v>
       </c>
       <c r="I35" t="n">
-        <v>279.6276276276276</v>
+        <v>3.513513513513506</v>
       </c>
       <c r="J35" t="n">
-        <v>3.513513513513506</v>
-      </c>
-      <c r="K35" t="n">
         <v>1.256497272219595</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69862,18 +69875,15 @@
         <v>5.494791666666651</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>325.2372372372372</v>
       </c>
       <c r="I36" t="n">
-        <v>325.2372372372372</v>
+        <v>3.168168168168159</v>
       </c>
       <c r="J36" t="n">
-        <v>3.168168168168159</v>
-      </c>
-      <c r="K36" t="n">
         <v>0.974109912837935</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69906,18 +69916,15 @@
         <v>10</v>
       </c>
       <c r="H37" t="n">
-        <v>-20.18856261191218</v>
+        <v>330.9376876876877</v>
       </c>
       <c r="I37" t="n">
-        <v>330.9376876876877</v>
+        <v>5.870870870870871</v>
       </c>
       <c r="J37" t="n">
-        <v>5.870870870870871</v>
-      </c>
-      <c r="K37" t="n">
         <v>1.774010966200781</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -69950,18 +69957,15 @@
         <v>8.482142857142861</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>291.3393393393393</v>
       </c>
       <c r="I38" t="n">
-        <v>291.3393393393393</v>
+        <v>4.279279279279281</v>
       </c>
       <c r="J38" t="n">
-        <v>4.279279279279281</v>
-      </c>
-      <c r="K38" t="n">
         <v>1.46882988373052</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -69994,18 +69998,15 @@
         <v>5.999999999999985</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>234.9286786786787</v>
       </c>
       <c r="I39" t="n">
-        <v>234.9286786786787</v>
+        <v>2.477477477477471</v>
       </c>
       <c r="J39" t="n">
-        <v>2.477477477477471</v>
-      </c>
-      <c r="K39" t="n">
         <v>1.054565790524884</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70038,18 +70039,15 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
+        <v>296.746996996997</v>
+      </c>
+      <c r="I40" t="n">
         <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>296.746996996997</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70082,18 +70080,15 @@
         <v>7.224669603524235</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>192.0217717717718</v>
       </c>
       <c r="I41" t="n">
-        <v>192.0217717717718</v>
+        <v>2.462462462462464</v>
       </c>
       <c r="J41" t="n">
-        <v>2.462462462462464</v>
-      </c>
-      <c r="K41" t="n">
         <v>1.282387116701138</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70126,18 +70121,15 @@
         <v>8.47272727272726</v>
       </c>
       <c r="H42" t="n">
-        <v>-11.92558823585216</v>
+        <v>229.8235735735736</v>
       </c>
       <c r="I42" t="n">
-        <v>229.8235735735736</v>
+        <v>3.498498498498493</v>
       </c>
       <c r="J42" t="n">
-        <v>3.498498498498493</v>
-      </c>
-      <c r="K42" t="n">
         <v>1.52225398121682</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70170,18 +70162,15 @@
         <v>5.494791666666651</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>337.2492492492493</v>
       </c>
       <c r="I43" t="n">
-        <v>337.2492492492493</v>
+        <v>3.168168168168159</v>
       </c>
       <c r="J43" t="n">
-        <v>3.168168168168159</v>
-      </c>
-      <c r="K43" t="n">
         <v>0.939414446502348</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70214,18 +70203,15 @@
         <v>6.543909348441922</v>
       </c>
       <c r="H44" t="n">
-        <v>-10.30545226499976</v>
+        <v>291.6268768768769</v>
       </c>
       <c r="I44" t="n">
-        <v>291.6268768768769</v>
+        <v>3.468468468468466</v>
       </c>
       <c r="J44" t="n">
-        <v>3.468468468468466</v>
-      </c>
-      <c r="K44" t="n">
         <v>1.189351443054006</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70258,18 +70244,15 @@
         <v>2.210526315789464</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>231.9181681681682</v>
       </c>
       <c r="I45" t="n">
-        <v>231.9181681681682</v>
+        <v>0.9459459459459417</v>
       </c>
       <c r="J45" t="n">
-        <v>0.9459459459459417</v>
-      </c>
-      <c r="K45" t="n">
         <v>0.4078791900684635</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70302,18 +70285,15 @@
         <v>8.214285714285721</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>283.2312312312313</v>
       </c>
       <c r="I46" t="n">
-        <v>283.2312312312313</v>
+        <v>4.144144144144147</v>
       </c>
       <c r="J46" t="n">
-        <v>4.144144144144147</v>
-      </c>
-      <c r="K46" t="n">
         <v>1.463166376860767</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70346,18 +70326,15 @@
         <v>10</v>
       </c>
       <c r="H47" t="n">
-        <v>-18.12043267312907</v>
+        <v>341.7484984984985</v>
       </c>
       <c r="I47" t="n">
-        <v>341.7484984984985</v>
+        <v>5.870870870870871</v>
       </c>
       <c r="J47" t="n">
-        <v>5.870870870870871</v>
-      </c>
-      <c r="K47" t="n">
         <v>1.717892220935878</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70390,18 +70367,15 @@
         <v>8.254545454545434</v>
       </c>
       <c r="H48" t="n">
-        <v>-11.26325780265245</v>
+        <v>250.243993993994</v>
       </c>
       <c r="I48" t="n">
-        <v>250.243993993994</v>
+        <v>3.4084084084084</v>
       </c>
       <c r="J48" t="n">
-        <v>3.4084084084084</v>
-      </c>
-      <c r="K48" t="n">
         <v>1.362034050851268</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70434,18 +70408,15 @@
         <v>8.489583333333313</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>325.5375375375375</v>
       </c>
       <c r="I49" t="n">
-        <v>325.5375375375375</v>
+        <v>4.894894894894882</v>
       </c>
       <c r="J49" t="n">
-        <v>4.894894894894882</v>
-      </c>
-      <c r="K49" t="n">
         <v>1.503634552230541</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70478,18 +70449,15 @@
         <v>7.392473118279567</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>350.4714714714715</v>
       </c>
       <c r="I50" t="n">
-        <v>350.4714714714715</v>
+        <v>4.129129129129128</v>
       </c>
       <c r="J50" t="n">
-        <v>4.129129129129128</v>
-      </c>
-      <c r="K50" t="n">
         <v>1.178164120404088</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70522,18 +70490,15 @@
         <v>9.999999999999989</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>380.4632132132131</v>
       </c>
       <c r="I51" t="n">
-        <v>380.4632132132131</v>
+        <v>6.351351351351345</v>
       </c>
       <c r="J51" t="n">
-        <v>6.351351351351345</v>
-      </c>
-      <c r="K51" t="n">
         <v>1.669373314100678</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70550,7 +70515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70576,20 +70541,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -70622,9 +70582,6 @@
       <c r="H2" t="n">
         <v>50</v>
       </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -70645,15 +70602,12 @@
         <v>6.755412476980427</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.090469257287507</v>
+        <v>319.7127627627628</v>
       </c>
       <c r="G3" t="n">
-        <v>319.7127627627628</v>
+        <v>3.808408408408405</v>
       </c>
       <c r="H3" t="n">
-        <v>3.808408408408405</v>
-      </c>
-      <c r="I3" t="n">
         <v>1.162405494661574</v>
       </c>
     </row>
@@ -70676,15 +70630,12 @@
         <v>2.683672748421583</v>
       </c>
       <c r="F4" t="n">
-        <v>6.784330659740201</v>
+        <v>61.84048792451369</v>
       </c>
       <c r="G4" t="n">
-        <v>61.84048792451369</v>
+        <v>1.765949821954865</v>
       </c>
       <c r="H4" t="n">
-        <v>1.765949821954865</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.4587607714362809</v>
       </c>
     </row>
@@ -70707,17 +70658,14 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-27.51790088311122</v>
+        <v>185.4151651651651</v>
       </c>
       <c r="G5" t="n">
-        <v>185.4151651651651</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -70738,15 +70686,12 @@
         <v>5.153327289351743</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>278.7391141141141</v>
       </c>
       <c r="G6" t="n">
-        <v>278.7391141141141</v>
+        <v>2.533783783783782</v>
       </c>
       <c r="H6" t="n">
-        <v>2.533783783783782</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.8664231572755949</v>
       </c>
     </row>
@@ -70769,15 +70714,12 @@
         <v>7.308571360901901</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>325.3873873873873</v>
       </c>
       <c r="G7" t="n">
-        <v>325.3873873873873</v>
+        <v>3.79879879879879</v>
       </c>
       <c r="H7" t="n">
-        <v>3.79879879879879</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.269442194460366</v>
       </c>
     </row>
@@ -70800,15 +70742,12 @@
         <v>8.755801338074855</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>361.0960960960961</v>
       </c>
       <c r="G8" t="n">
-        <v>361.0960960960961</v>
+        <v>5.225225225225222</v>
       </c>
       <c r="H8" t="n">
-        <v>5.225225225225222</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.534024712985602</v>
       </c>
     </row>
@@ -70831,15 +70770,12 @@
         <v>10</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>450.0750750750751</v>
       </c>
       <c r="G9" t="n">
-        <v>450.0750750750751</v>
+        <v>6.936936936936933</v>
       </c>
       <c r="H9" t="n">
-        <v>6.936936936936933</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.774010966200781</v>
       </c>
     </row>
